--- a/docs/workbook-split/dateien/Monatsanalyse.xlsx
+++ b/docs/workbook-split/dateien/Monatsanalyse.xlsx
@@ -656,17 +656,14 @@
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>INDEX('[GuV.xlsx]GuV'!$F$7:$Q$7,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",INDEX('[GuV.xlsx]GuV'!$F$7:$Q$7,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>IF(ISNUMBER(E7),D7-E7,"n.a.")</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>31042.87</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -694,17 +691,14 @@
           <t>Bestandsveränderung</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>INDEX('[GuV.xlsx]GuV'!$F$8:$Q$8,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",INDEX('[GuV.xlsx]GuV'!$F$8:$Q$8,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>IF(ISNUMBER(E8),D8-E8,"n.a.")</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1022525.14</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1022525.14</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -732,29 +726,23 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <f>INDEX('[GuV.xlsx]GuV'!$F$9:$Q$9,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",INDEX('[GuV.xlsx]GuV'!$F$9:$Q$9,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>IF(ISNUMBER(E9),D9-E9,"n.a.")</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$182:$D$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>D9-G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>IF(G9=0,"n.a.",H9/ABS(G9))</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1876864.98</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-991482.27</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1483000</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-597617.29</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-0.4029786176668915</v>
       </c>
       <c r="J9" s="1" t="n"/>
       <c r="K9" s="1" t="n"/>
@@ -767,29 +755,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D10" s="9">
-        <f>INDEX('[GuV.xlsx]GuV'!$F$20:$Q$20,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",INDEX('[GuV.xlsx]GuV'!$F$20:$Q$20,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F10" s="9">
-        <f>IF(ISNUMBER(E10),D10-E10,"n.a.")</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$182:$G$193,'[D Finanzen.xlsx]D Finanzen'!$A$182:$A$193,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$182:$B$193,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
-        <f>D10-G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="10">
-        <f>IF(G10=0,"n.a.",H10/ABS(G10))</f>
-        <v/>
+      <c r="D10" s="9" t="n">
+        <v>-1453149.19</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>-1314906.82</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>-1578149.19</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>-12.62519352</v>
       </c>
       <c r="J10" s="1" t="n"/>
       <c r="K10" s="1" t="n"/>
@@ -802,17 +784,14 @@
           <t>Neutrales Ergebnis</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>INDEX('[GuV.xlsx]GuV'!$F$24:$Q$24,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",INDEX('[GuV.xlsx]GuV'!$F$24:$Q$24,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>IF(ISNUMBER(E11),D11-E11,"n.a.")</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>312223.42</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1492.2</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>310731.22</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -840,17 +819,14 @@
           <t>EBITDA nach neutral</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <f>SUM(D10:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",SUM(E10:E11))</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>IF(ISNUMBER(E12),D12-E12,"n.a.")</f>
-        <v/>
+      <c r="D12" s="6" t="n">
+        <v>-1140925.77</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-136750.17</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-1004175.6</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1766,6 +1742,8 @@
       <c r="J60" s="1" t="n"/>
       <c r="K60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
